--- a/livrables/voies_par_troncon.xlsx
+++ b/livrables/voies_par_troncon.xlsx
@@ -565,7 +565,7 @@
         <v>2.1</v>
       </c>
       <c r="F3" t="n">
-        <v>68.2</v>
+        <v>68.3</v>
       </c>
       <c r="G3" t="n">
         <v>30.6</v>
@@ -596,16 +596,16 @@
         <v>445.9</v>
       </c>
       <c r="C4" t="n">
-        <v>111.2</v>
+        <v>111.3</v>
       </c>
       <c r="D4" t="n">
         <v>307.3</v>
       </c>
       <c r="E4" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="F4" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
         <v>68.90000000000001</v>
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -642,7 +642,7 @@
         <v>505.3</v>
       </c>
       <c r="E5" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -651,7 +651,7 @@
         <v>93.59999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I5" t="n">
         <v>3.8</v>
@@ -660,7 +660,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1052</v>
+        <v>1684.9</v>
       </c>
     </row>
     <row r="9">
@@ -700,10 +700,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>445.4</v>
+        <v>760.4</v>
       </c>
       <c r="C9" t="n">
-        <v>42.3</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="10">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>575.9</v>
+        <v>847.1</v>
       </c>
       <c r="C10" t="n">
-        <v>54.7</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="11">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="12">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>404.8</v>
+        <v>699.4</v>
       </c>
     </row>
     <row r="13">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>400.2</v>
+        <v>694.9</v>
       </c>
     </row>
     <row r="14">
@@ -760,7 +760,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>'400-405</t>
+          <t>'695-699</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11.7</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="16">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.8</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="18">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>391.2</v>
+        <v>-241.7</v>
       </c>
     </row>
   </sheetData>
